--- a/all_channels.xlsx
+++ b/all_channels.xlsx
@@ -11,6 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Belal Assaad" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arabic 101" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khalid Mehmood Abbasi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yaqeen Institute" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarteel AI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ali Hammuda" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Towards Eternity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bayyinah Institute" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The Home Institute" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,110 +450,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Allah’s Words to Musa Were Meant for You Too | Tasmania | Abu Bakr Zoud</t>
+          <t>2 Things To Do At The Time Of Sahoor (Pre Dawn Meal) | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OFQLIlCQR4s</t>
+          <t>https://www.youtube.com/watch?v=t0CPrAWAKtk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60m 39s</t>
+          <t>4m 8s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Understanding Surah Al-Maoun (Small Acts Of Kindness) | Friday Khutbah | Abu Bakr Zoud</t>
+          <t>Avoid This Common Mistake at Maghrib During Ramadan | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ngWbcOmEpoc</t>
+          <t>https://www.youtube.com/watch?v=of5emONPLuM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32m 7s</t>
+          <t>3m 19s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tafseer Surah Al-Haaqqah (The Inevitable Reality) | Part 5/5 | Ayaat 25-52 | Abu Bakr Zoud</t>
+          <t>The 4 Major Mistakes Of The Prayer | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rYNDwICyAcA</t>
+          <t>https://www.youtube.com/watch?v=_Dh5ul3zlvU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>81m 42s</t>
+          <t>64m 55s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tafseer Surah Al-Haaqqah (The Inevitable Reality) | Part 4/5 | Ayaat 18-24 | Abu Bakr Zoud</t>
+          <t>The Quran &amp; Ramadan | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JRKVGsQKIOM</t>
+          <t>https://www.youtube.com/watch?v=5K7VQgYY998</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>79m 35s</t>
+          <t>12m 0s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tafseer Surah Al-Haaqqah (The Inevitable Reality) | Part 3/5 | ayaat 9-17 | Abu Bakr Zoud</t>
+          <t>The Night Prayer During Ramadan | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=H03lC8v28wA</t>
+          <t>https://www.youtube.com/watch?v=8ChMYN2GQEU</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>75m 46s</t>
+          <t>10m 32s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ruh vs Nafs Values| Lesson 5 (Pt 2 ): Victimhood vs. Accountability| H.O.M.E Method| Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OgwtTtUz2Ec</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>60m 8s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ruh vs Nafs Values| Lesson 5 (Pt 1): Victimhood vs. Accountability| H.O.M.E Method| Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ekfBwsDXGKQ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>43m 41s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4 Spiritual Values of Worry &amp; Fear! | Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=94562ViNrI4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5m 25s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ruh Values vs Nafs Values | Lesson 4: Balance Vs. Excess | The H.O.M.E. Method | Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3nvC0n3BBFU</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>37m 23s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Your Body Tells You When You Lose Focus in Your IBADAH! | Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Eg4dMrAkIJo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5m 0s</t>
         </is>
       </c>
     </row>
@@ -590,110 +742,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A Reflection on Self-Worth and Existence - The Fashioner (Al Musawwir)</t>
+          <t>And He is the Best Disposer of affairs - Al Haseeb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=r8aS4qHUdCE</t>
+          <t>https://www.youtube.com/watch?v=Zfxhyrv9wfc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24m 3s</t>
+          <t>51m 10s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nothing can overcome The Compeller, The Mender, The Most High (Al Jabbar)</t>
+          <t>The DOs and DON'Ts of Ramadan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wLOIL8c-5nE</t>
+          <t>https://www.youtube.com/watch?v=zU-YGDt8W1g</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42m 42s</t>
+          <t>67m 31s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Manifest &amp; The Hidden (Az-Zahir wal-Batin)</t>
+          <t>The Most Generous, The Most Noble (Al Kareem)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7SGtcWJH89Y</t>
+          <t>https://www.youtube.com/watch?v=0VJyEHpLjTk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67m 17s</t>
+          <t>18m 19s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The All-Knowing, The All-Wise Knows Why (Al-'Aleem, Al Hakeem)</t>
+          <t>Allah is Ḥayiyy - He will not turn you away</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=X7IG3V04gEU</t>
+          <t>https://www.youtube.com/watch?v=O6ijRB0xsYs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52m 57s</t>
+          <t>49m 13s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The 'Ever Near' is always with you (Al-Qareeb)</t>
+          <t>A Reflection on Self-Worth and Existence - The Fashioner (Al Musawwir)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=oFTvfZ77x_k</t>
+          <t>https://www.youtube.com/watch?v=r8aS4qHUdCE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>79m 58s</t>
+          <t>24m 3s</t>
         </is>
       </c>
     </row>
@@ -736,110 +888,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Wait!! Doesn't Allah Already Know Everything? How Is This Possible? | Arabic101</t>
+          <t>🚫You MUST Avoid This 'NEW' Quran Content🚫 | Arabic101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=MaW0Q76r-AY</t>
+          <t>https://www.youtube.com/watch?v=M6SV8auUpBo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7m 35s</t>
+          <t>9m 40s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Why Read the Whole Quran if One Surah = 1/3 ? | Arabic101</t>
+          <t>Wait!! Doesn't Allah Already Know Everything? How Is This Possible? | Arabic101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Up5WNJAHM_w</t>
+          <t>https://www.youtube.com/watch?v=MaW0Q76r-AY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8m 7s</t>
+          <t>7m 35s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A Rule Only Mastered by Advanced Learners | Dammah Continuation | Arabic101</t>
+          <t>Why Read the Whole Quran if One Surah = 1/3 ? | Arabic101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x5YPUJONVhg</t>
+          <t>https://www.youtube.com/watch?v=Up5WNJAHM_w</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6m 41s</t>
+          <t>8m 7s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A Mind-Blowing Gem Hidden in the Most Common Arabic Word | Arabic101</t>
+          <t>A Rule Only Mastered by Advanced Learners | Dammah Continuation | Arabic101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8KYagLT0hb8</t>
+          <t>https://www.youtube.com/watch?v=x5YPUJONVhg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8m 36s</t>
+          <t>6m 41s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>We MUST Stop Saying This | Arabic101</t>
+          <t>A Mind-Blowing Gem Hidden in the Most Common Arabic Word | Arabic101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0BNClIQv_k0</t>
+          <t>https://www.youtube.com/watch?v=8KYagLT0hb8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8m 11s</t>
+          <t>8m 36s</t>
         </is>
       </c>
     </row>
@@ -882,110 +1034,840 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rah-e-Hidayat LEC 130 | Surah Nuh Ayat 01to 03 | Allah’s Law Behind the Destruction of Nations</t>
+          <t>Why is the US Not Attacking Iran? | Imran Khan’s Health | PTI’s Positive Politics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3FfhstfsiS8</t>
+          <t>https://www.youtube.com/watch?v=Mto-rq6_pds</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42m 50s</t>
+          <t>78m 30s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rising Pressure on Iran &amp; the Muslim World | A Qur’anic Perspective | Khalid Mehmood Abbasi</t>
+          <t>Shaitan, Dajjal &amp; the Epstein Network | Hidden Evil in the Modern World?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m_nwhpDwbJs</t>
+          <t>https://www.youtube.com/watch?v=oDjaQ0iRPsc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>62m 12s</t>
+          <t>110m 11s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pakistan Ek Khudai Raaz Ep 29 | Global Powers vs Pakistan’s Survival | Divine Plan Revealed</t>
+          <t>Bangladesh Elections: Rise of Islamic Forces | Cricket Diplomacy &amp; India Under Pressure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=59LcLHunzEY</t>
+          <t>https://www.youtube.com/watch?v=RdAAes5_wVA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28m 3s</t>
+          <t>65m 11s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>World War III: Global Powers Face Off? | US Pressure, Iranian Resistance &amp; Saudi Policy Shift</t>
+          <t>Rah-e-Hidayat LEC 131 | The True Meaning of Worship (Ibadah) &amp; the Message of Obedience (Ita‘at)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zYjbuZw86Vs</t>
+          <t>https://www.youtube.com/watch?v=vgF7I3Be80E</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>96m 40s</t>
+          <t>42m 33s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pakistan Ek Khudai Raaz Ep 28 | Pakistan’s Future Wars &amp; Ultimate Victory | World War 3 Prophecies</t>
+          <t>Relevance of Maududi’s Thought in a Changing World | Islamic Ideology &amp; Modern Challenges</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t4PmXsbaqUM</t>
+          <t>https://www.youtube.com/watch?v=WZ6E_jBEa0M</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28m 25s</t>
+          <t>64m 6s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>When Allah Goes To War For You | Dr. Suleiman Hani | Juz 10 Qur’an 30 for 30 S7 | Ramadan Series</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9gwe-HMwZv0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>31m 53s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Al-Wadud, Al-Muhsin, and Ash-Shakur | Allah's Names | Dr. Omar Suleiman | Ep. 10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t--rezLMP1c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>16m 41s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>How To Memorize Allah’s Names | Dr. Haifaa Younis | Juz 9 Qur’an 30 for 30 S7 | Ramadan Series</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0Nguw7xrDWA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>30m 11s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Will Allah Forgive Me? | Allah’s Names Ep. 9 | Dr. Omar Suleiman</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6aeEn3GWLQI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>15m 38s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Whose Validation Do You Need? | Sh. Shabbir Hassan | Juz 8 Qur’an 30 for 30 S7 | Ramadan Series</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JWSQ6IR98-c</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>26m 32s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The Injil of Isa | Wahy Ep. 10 | Ustadha Fatima Barkatulla | Ramadan Series 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wZ7IaBWvfa0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>11m 36s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The Zabur of Dawud | Wahy Ep. 9 | Ustadh Dawoud Yahya | Ramadan Series 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yhBW4gVdJE0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9m 40s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Women &amp; Wahy | Wahy Ep. 8 | Ustadha Fatima Barkatulla | Ramadan Series 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=V-QuHdAb6-I</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7m 47s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>The Scrolls of Ibrahim | Wahy Ep. 7 | Ustadh Dawoud Yahya | Ramadan Series 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Z1J99LHmvaY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11m 11s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>The Jinn &amp; The Whispering Stars | Wahy Ep.6 | Ustadha Fatima Barkatulla | Ramadan Series 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ol-ZYRgqR8Q</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8m 33s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Clinging To What Can't Stay | Episode 5 | Tomorrow As though You can See it</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wfIZKLiFieI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>11m 28s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Your Last Entourage | Episode 4 | Tomorrow As though You can See it</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PBLQ0nfi0W4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11m 21s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Longing at the Edge of Life | Episode 3 | Tomorrow As though You can See it</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CG8hrK4mfXo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>11m 54s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A Rehearsal | Episode 2 | Tomorrow As though You can See it</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6TVmPzZyB3Y</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9m 25s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Your First Glimpse of Tomorrow | Episode 1 | Tomorrow As though You can See it</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WqdI7l9mK8A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9m 13s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No Food, No Mercy to Prophet’s Family! - AI Visualized - O Messenger | Ep. 4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jx9syOUU1Ms</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>58m 57s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hamza and Umar (ra) Become Muslims! - AI Visualized - O Messenger | Ep. 3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dAZPkwAo0lE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>45m 24s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>The Hardest Days of Islam - AI Visualized - O Messenger | Ep. 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Qnzam5KcopM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>46m 16s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Life of Prophet Muhammad - The World’s First AI-Visualized Sirah Series! - O Messenger | Ep. 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DW-00ckCAPI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>58m 43s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>The World's First AI-Visualized Sirah Series - Official Trailer - O MESSENGER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sQMC7fkjmOA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2m 38s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ep 9: Beauty, Care and Being Loved | Surah Ar-Rahman: A Deeper Look | Nouman Ali Khan | Ramadan 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RSySaKOxvls</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>25m 14s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[Urdu] Ep 9: Shukr Is Easier Than You Think | Allamal Quran: A Study of Surah Ar-Rahman | Ramada 26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xY-zVjkPbbw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>25m 31s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ep 8: Don’t Violate the Balance | Surah Ar-Rahman: A Deeper Look | Ramadan 26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2Ec6jH1oWts</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>28m 37s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[Urdu] Ep 8: فَبِأَيِّ آلَاءِ رَبِّكُمَا تُكَذِّبَان Why Does Allah Keep Asking This Question?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aN8LqGIDy9U</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21m 8s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ep 7: Everything Lowers Itself, Everything Is Measured | Surah Ar-Rahman: A Deeper Look | Ramadan 26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kdLlyP5KBxU</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>32m 41s</t>
         </is>
       </c>
     </row>

--- a/all_channels.xlsx
+++ b/all_channels.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abu Bakr Zoud" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Belal Assaad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arabic 101" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khalid Mehmood Abbasi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yaqeen Institute" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarteel AI" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ali Hammuda" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Towards Eternity" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bayyinah Institute" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The Home Institute" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Abu Bakr Zoud" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Belal Assaad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Arabic 101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Khalid Mehmood Abbasi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Yaqeen Institute" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tarteel AI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ali Hammuda" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Mohamed Hoblos" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Towards Eternity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Bayyinah Institute" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="The Home Institute" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Safina Society" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Zabeel Al Ilm" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Rihla" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,110 +454,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2 Things To Do At The Time Of Sahoor (Pre Dawn Meal) | Abu Bakr Zoud</t>
+          <t>Hajar's Journey Of Faith Between Safa And Marwa | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t0CPrAWAKtk</t>
+          <t>https://www.youtube.com/watch?v=XTQ2Gbp0klY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4m 8s</t>
+          <t>33m 8s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Avoid This Common Mistake at Maghrib During Ramadan | Abu Bakr Zoud</t>
+          <t>Two Principles for Success in This Life and the Next | Friday Khutbah | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=of5emONPLuM</t>
+          <t>https://www.youtube.com/watch?v=SsZIqAJ83VM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3m 19s</t>
+          <t>26m 52s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The 4 Major Mistakes Of The Prayer | Abu Bakr Zoud</t>
+          <t>Ibrahim's Greatest Test The Story Of The Sacrifice | UK Tour | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_Dh5ul3zlvU</t>
+          <t>https://www.youtube.com/watch?v=W7kgSAXwUTU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64m 55s</t>
+          <t>31m 42s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Quran &amp; Ramadan | Abu Bakr Zoud</t>
+          <t>The Incredible Results Of Istighathah (Turning to Allah for Urgent Help), Heres How You Can Do It.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5K7VQgYY998</t>
+          <t>https://www.youtube.com/watch?v=vjSAHcCkUD0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12m 0s</t>
+          <t>3m 14s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Night Prayer During Ramadan | Abu Bakr Zoud</t>
+          <t>The Quran, A Guidance For Mankind | Abu Bakr Zoud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8ChMYN2GQEU</t>
+          <t>https://www.youtube.com/watch?v=sl77ymGjfv4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10m 32s</t>
+          <t>63m 56s</t>
         </is>
       </c>
     </row>
@@ -596,110 +600,694 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ruh vs Nafs Values| Lesson 5 (Pt 2 ): Victimhood vs. Accountability| H.O.M.E Method| Dr. Marwa Assar</t>
+          <t>Why Did Allah Mention Business in the Quran? | Nouman Ali Khan | Khutbah Highlights</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OgwtTtUz2Ec</t>
+          <t>https://www.youtube.com/watch?v=dpT9hUAIO5U</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60m 8s</t>
+          <t>11m 56s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ruh vs Nafs Values| Lesson 5 (Pt 1): Victimhood vs. Accountability| H.O.M.E Method| Dr. Marwa Assar</t>
+          <t>The Prayer That Sealed Pharaoh's Fate Before He Even Knew It | Story Night: Pharaoh Shall Drown</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ekfBwsDXGKQ</t>
+          <t>https://www.youtube.com/watch?v=DBx3z02V0Z0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43m 41s</t>
+          <t>10m 27s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4 Spiritual Values of Worry &amp; Fear! | Dr. Marwa Assar</t>
+          <t>When Pharaoh Started Losing His Mind | Story Night: Pharaoh Shall Drown | Nouman Ali Khan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=94562ViNrI4</t>
+          <t>https://www.youtube.com/watch?v=0G4ASyK90oE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5m 25s</t>
+          <t>17m 30s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ruh Values vs Nafs Values | Lesson 4: Balance Vs. Excess | The H.O.M.E. Method | Dr. Marwa Assar</t>
+          <t>How Allah Exposes Sneaky Backbiters | Nouman Ali Khan | Khutbah Highlights</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3nvC0n3BBFU</t>
+          <t>https://www.youtube.com/watch?v=P-B7aRn1lwI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37m 23s</t>
+          <t>11m 10s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Your Body Tells You When You Lose Focus in Your IBADAH! | Dr. Marwa Assar</t>
+          <t>Pharaoh Finally Snapped | Story Night: Pharaoh Shall Drown | Nouman Ali Khan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Eg4dMrAkIJo</t>
+          <t>https://www.youtube.com/watch?v=bRX5WMWifJs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5m 0s</t>
+          <t>15m 3s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5 Powerful Ways to Heal &amp; Break the Chains Keeping You Stuck! (Part 1) | Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=S9hWAxm9U_c</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>58m 17s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Navigating Disappointments &amp; the Grief of an Unplanned Life Through the Divine | Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g3cNBfo2a8k</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>51m 34s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>The Hidden Blessing of Trauma &amp; Brokenness That You Won't Hear About | Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7d59V2gvV6g</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4m 4s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A Prophetic Dua For Anxiety: A Neuropsychological Miracle! | Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5NNkEp8ab5U</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5m 50s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>From Broken to WHOLE: Heal What Life Broke Through Al-Jabbar (The Mender) | Dr. Marwa Assar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YHyrr2s-ilE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30m 48s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Weight Loss Drugs, Looksmaxxing &amp; Islam's View of the Body | Dr Shadee Elmasry</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VFWL3jCWBVw</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7m 3s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Is Your Aqida Just Greek Philosophy? | Dr Shadee Elmasry</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GCAAfU0pNtY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7m 45s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Marriage Red Flags Most Muslims Ignore | Dr Shadee Elmasry</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RY1zQ4kWd5Y</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8m 21s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Islamic Finance Expert: How Riba Is a War</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ic-PXHb2g4E</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8m 14s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>How to Make $10K for Hajj (Even If You’re Broke)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sWIaksPBis8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8m 13s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The Invisible Habits That Feed Depression - Shaykh Hamza Yusuf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7vhnxomUd_c</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>18m 55s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The 5 Most Important Islamic Rulings Explained - Shaykh Hamza Yusuf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HidhVRaaKd8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>15m 5s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>The Mistake Most Muslim Students Make About Their Studies - Shaykh Hamza Yusuf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fhXv88atHQA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12m 13s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Why People Hurt their Own Souls  - Shaykh Hamza Yusuf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oQLo38y76fQ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11m 27s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Most Muslims Get This Wrong - The Prophet's ﷺ Stance on Learning</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p6tp5XAx7Jk</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19m 20s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upload Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The Sin That Makes You Look Like A Hypocrite - Shaykh Abdal Hakim Murad</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W2tqupoGx-o</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>54m 2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The Prophet's Way of Speaking | Forgotten Adab of Speaking  - Shaykh Abdal Hakim Murad</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kj-1iNi2c9c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>79m 19s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ghazzali on Hidden Disease Of Religious Performance [ Show OFF ]  - Shaykh Abdal Hakim Murad</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z8Gol2zWquc</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>24m 13s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ghazzali's Warning about Speech That Allah Does Not Love - Shaykh Abdal Hakim Murad</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QN3bdBxreYg</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>35m 23s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>The Silent Door To Inner Peace  - Shaykh Abdal Hakim Murad</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qhoJZ0lvDf0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>16m 27s</t>
         </is>
       </c>
     </row>
@@ -742,110 +1330,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>And He is the Best Disposer of affairs - Al Haseeb</t>
+          <t>The Cure for a lonely heart - Al Wadud (The Most Loving)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Zfxhyrv9wfc</t>
+          <t>https://www.youtube.com/watch?v=_4ve9yWAvHQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51m 10s</t>
+          <t>58m 59s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>The DOs and DON'Ts of Ramadan</t>
+          <t>Living by Allah’s Name ‘The Holy’- Al Quddus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zU-YGDt8W1g</t>
+          <t>https://www.youtube.com/watch?v=dW2BQJvNdKs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>67m 31s</t>
+          <t>59m 29s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Most Generous, The Most Noble (Al Kareem)</t>
+          <t>How do you react to Good and Bad? (The Benefactor, The Detractor)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0VJyEHpLjTk</t>
+          <t>https://www.youtube.com/watch?v=oKVgn6e-8t0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18m 19s</t>
+          <t>93m 41s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Allah is Ḥayiyy - He will not turn you away</t>
+          <t>The Secret to Inner Peace - Al-Mu’min</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=O6ijRB0xsYs</t>
+          <t>https://www.youtube.com/watch?v=KSHD0K_w4h8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49m 13s</t>
+          <t>72m 32s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A Reflection on Self-Worth and Existence - The Fashioner (Al Musawwir)</t>
+          <t>You Are Never Alone. He Protects, Hears &amp; Sees you (Al-Waliy, As-Samii' &amp; Al-Baseer)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=r8aS4qHUdCE</t>
+          <t>https://www.youtube.com/watch?v=QlQ2AdcmvU0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24m 3s</t>
+          <t>71m 2s</t>
         </is>
       </c>
     </row>
@@ -888,110 +1476,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>🚫You MUST Avoid This 'NEW' Quran Content🚫 | Arabic101</t>
+          <t>Stop Running Out of Breath While Reciting Quran | Lesson 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M6SV8auUpBo</t>
+          <t>https://www.youtube.com/watch?v=65d6Du0PpWw</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9m 40s</t>
+          <t>10m 24s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wait!! Doesn't Allah Already Know Everything? How Is This Possible? | Arabic101</t>
+          <t>Basmalah vs Tasmiyah — A Mistake SO MANY Muslims Makes | Arabic101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=MaW0Q76r-AY</t>
+          <t>https://www.youtube.com/watch?v=lJDKhEro6uA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7m 35s</t>
+          <t>6m 10s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Why Read the Whole Quran if One Surah = 1/3 ? | Arabic101</t>
+          <t>Tajweed is Only 50% of Quran Learning .. Here's the Rest | Lesson 1 | Arabic101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Up5WNJAHM_w</t>
+          <t>https://www.youtube.com/watch?v=TuvHtvj0tUA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8m 7s</t>
+          <t>8m 43s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A Rule Only Mastered by Advanced Learners | Dammah Continuation | Arabic101</t>
+          <t>Has Quran Dramatization Gone Too Far? | Arabic101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x5YPUJONVhg</t>
+          <t>https://www.youtube.com/watch?v=1gmR07cvAuo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6m 41s</t>
+          <t>21m 29s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A Mind-Blowing Gem Hidden in the Most Common Arabic Word | Arabic101</t>
+          <t>Why Neuroscientists Are Telling People to Learn Arabic | Arabic101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8KYagLT0hb8</t>
+          <t>https://www.youtube.com/watch?v=SmbVPUiPdp0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8m 36s</t>
+          <t>7m 35s</t>
         </is>
       </c>
     </row>
@@ -1034,110 +1622,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Why is the US Not Attacking Iran? | Imran Khan’s Health | PTI’s Positive Politics</t>
+          <t>Pakistan’s Unique Position in the Muslim Ummah &amp; Its Greater Responsibility | Khalid Mehmood Abbasi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Mto-rq6_pds</t>
+          <t>https://www.youtube.com/watch?v=6xgbkQROl80</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>78m 30s</t>
+          <t>55m 42s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shaitan, Dajjal &amp; the Epstein Network | Hidden Evil in the Modern World?</t>
+          <t>Glad Tidings of Islam’s Global Dominance | Insights from Surah Al-Anbiya</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=oDjaQ0iRPsc</t>
+          <t>https://www.youtube.com/watch?v=4B_XJinVbr4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>110m 11s</t>
+          <t>32m 14s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bangladesh Elections: Rise of Islamic Forces | Cricket Diplomacy &amp; India Under Pressure</t>
+          <t>Beyond the Headlines: Understanding the Current World Situation | Global Crisis Explained</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RdAAes5_wVA</t>
+          <t>https://www.youtube.com/watch?v=WGcSdJhlpKM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65m 11s</t>
+          <t>56m 50s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rah-e-Hidayat LEC 131 | The True Meaning of Worship (Ibadah) &amp; the Message of Obedience (Ita‘at)</t>
+          <t>The Contemporary Global Imperialist Agenda &amp; The Muslim Ummah’s Strategic Response Explained</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vgF7I3Be80E</t>
+          <t>https://www.youtube.com/watch?v=2B0F9qvrvWs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42m 33s</t>
+          <t>79m 17s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Relevance of Maududi’s Thought in a Changing World | Islamic Ideology &amp; Modern Challenges</t>
+          <t>Justice or Selective Accountability? One Constitution Avenue &amp; Saad Riaz Case | Tazkara o Tabsara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WZ6E_jBEa0M</t>
+          <t>https://www.youtube.com/watch?v=aIMldLmMVuA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>64m 6s</t>
+          <t>66m 16s</t>
         </is>
       </c>
     </row>
@@ -1180,110 +1768,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>When Allah Goes To War For You | Dr. Suleiman Hani | Juz 10 Qur’an 30 for 30 S7 | Ramadan Series</t>
+          <t>TRAILER: The Book of Heart Softeners | Dhul Hijjah 2026 | Dr. Omar Suleiman and Sh. Ali Hammuda</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9gwe-HMwZv0</t>
+          <t>https://www.youtube.com/watch?v=jOcDbMtwU6w</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31m 53s</t>
+          <t>1m 8s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Al-Wadud, Al-Muhsin, and Ash-Shakur | Allah's Names | Dr. Omar Suleiman | Ep. 10</t>
+          <t>When 43 Prophets Were Killed | Signs of the Hour Ep. 5 | Dr. Omar Suleiman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t--rezLMP1c</t>
+          <t>https://www.youtube.com/watch?v=tz5_bSu5PKA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16m 41s</t>
+          <t>64m 56s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>How To Memorize Allah’s Names | Dr. Haifaa Younis | Juz 9 Qur’an 30 for 30 S7 | Ramadan Series</t>
+          <t>You're Not A Lost Cause | Khutbah by Sh. Elshinawy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0Nguw7xrDWA</t>
+          <t>https://www.youtube.com/watch?v=S4ayL97D8_A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30m 11s</t>
+          <t>19m 55s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Will Allah Forgive Me? | Allah’s Names Ep. 9 | Dr. Omar Suleiman</t>
+          <t>Shaytan Prepared You For Dajjal | Signs of the Hour Ep. 4 | Dr. Omar Suleiman</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6aeEn3GWLQI</t>
+          <t>https://www.youtube.com/watch?v=dEpEMV77x44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15m 38s</t>
+          <t>29m 23s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Whose Validation Do You Need? | Sh. Shabbir Hassan | Juz 8 Qur’an 30 for 30 S7 | Ramadan Series</t>
+          <t>Salma (ra) and Ubaydullah (ra): A Legacy of Serving the Ahlul Bayt | The Firsts | Dr. Omar Suleiman</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JWSQ6IR98-c</t>
+          <t>https://www.youtube.com/watch?v=fQZqPATREck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26m 32s</t>
+          <t>11m 4s</t>
         </is>
       </c>
     </row>
@@ -1326,110 +1914,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The Injil of Isa | Wahy Ep. 10 | Ustadha Fatima Barkatulla | Ramadan Series 2026</t>
+          <t>Why You Keep Quitting The Quran (And How To Finally Stop)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wZ7IaBWvfa0</t>
+          <t>https://www.youtube.com/watch?v=zyFHCNDshCs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11m 36s</t>
+          <t>20m 5s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>The Zabur of Dawud | Wahy Ep. 9 | Ustadh Dawoud Yahya | Ramadan Series 2026</t>
+          <t>My Mum Made Me Memorize the Quran. Here's What She NEVER Told Me. 👀 | Ustadha Fatima Barkatulla</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yhBW4gVdJE0</t>
+          <t>https://www.youtube.com/watch?v=UyYmBuXuLMQ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9m 40s</t>
+          <t>42m 18s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Women &amp; Wahy | Wahy Ep. 8 | Ustadha Fatima Barkatulla | Ramadan Series 2026</t>
+          <t>How to Raise Hafiz Muslim Kids - Without Over-Parenting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=V-QuHdAb6-I</t>
+          <t>https://www.youtube.com/watch?v=jskOLhB1uis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7m 47s</t>
+          <t>19m 41s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Scrolls of Ibrahim | Wahy Ep. 7 | Ustadh Dawoud Yahya | Ramadan Series 2026</t>
+          <t>Your Final Rank in Jannah Depends On THIS! | Wahy Ep. 28 | Ust. Dawoud Yahya | Ramadan Series Finale</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Z1J99LHmvaY</t>
+          <t>https://www.youtube.com/watch?v=2rCLTg6SXOk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11m 11s</t>
+          <t>6m 53s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Jinn &amp; The Whispering Stars | Wahy Ep.6 | Ustadha Fatima Barkatulla | Ramadan Series 2026</t>
+          <t>The BEST Way to Repay Your Parents?!  | Wahy Ep. 27 | Ust. Dawoud Yahya | Ramadan Series 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ol-ZYRgqR8Q</t>
+          <t>https://www.youtube.com/watch?v=ry77Iqn3UNo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8m 33s</t>
+          <t>7m 41s</t>
         </is>
       </c>
     </row>
@@ -1472,110 +2060,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Clinging To What Can't Stay | Episode 5 | Tomorrow As though You can See it</t>
+          <t>Episode 16: Neediness before Allah (Al-iftiqār) | Change of Heart Series</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wfIZKLiFieI</t>
+          <t>https://www.youtube.com/watch?v=UTkh9vU5LAs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11m 28s</t>
+          <t>61m 9s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Your Last Entourage | Episode 4 | Tomorrow As though You can See it</t>
+          <t>Episode 15: Contentment (Al-Riḍā, Part 2) | Change of Heart Series</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PBLQ0nfi0W4</t>
+          <t>https://www.youtube.com/watch?v=MtdfwgVXeP0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11m 21s</t>
+          <t>62m 53s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Longing at the Edge of Life | Episode 3 | Tomorrow As though You can See it</t>
+          <t>Episode 14: Contentment (Al-Riḍā, Part 1) | Change of Heart Series</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CG8hrK4mfXo</t>
+          <t>https://www.youtube.com/watch?v=M6-pcWw-_EQ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11m 54s</t>
+          <t>71m 38s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A Rehearsal | Episode 2 | Tomorrow As though You can See it</t>
+          <t>Episode 13: Ever-Returning (Inābah) | Change of Heart Series</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6TVmPzZyB3Y</t>
+          <t>https://www.youtube.com/watch?v=vPyzKKorTZo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9m 25s</t>
+          <t>53m 40s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Your First Glimpse of Tomorrow | Episode 1 | Tomorrow As though You can See it</t>
+          <t>The Worship of Letting Go</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WqdI7l9mK8A</t>
+          <t>https://www.youtube.com/watch?v=4UdndVpRL0c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9m 13s</t>
+          <t>34m 30s</t>
         </is>
       </c>
     </row>
@@ -1618,110 +2206,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No Food, No Mercy to Prophet’s Family! - AI Visualized - O Messenger | Ep. 4</t>
+          <t>We Forgotten Why Are We Here ! Very Touching Speech ! (No Nasheed) Mohamed Hoblos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=jx9syOUU1Ms</t>
+          <t>https://www.youtube.com/watch?v=RrcgNW-a9Bc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58m 57s</t>
+          <t>37m 11s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hamza and Umar (ra) Become Muslims! - AI Visualized - O Messenger | Ep. 3</t>
+          <t>We Forgotten Why Are We Here ! Very Touching Speech ! Mohamed Hoblos</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dAZPkwAo0lE</t>
+          <t>https://www.youtube.com/watch?v=Ut3Y_fckKO4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45m 24s</t>
+          <t>37m 11s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Hardest Days of Islam - AI Visualized - O Messenger | Ep. 2</t>
+          <t>Ramadan &amp; Eid Alone ! Mohamed Hoblos</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Qnzam5KcopM</t>
+          <t>https://www.youtube.com/watch?v=dsw3keIKWok</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46m 16s</t>
+          <t>2m 58s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Life of Prophet Muhammad - The World’s First AI-Visualized Sirah Series! - O Messenger | Ep. 1</t>
+          <t>Don't Stop ! Push Yourself the Whole Ramadan ! (No Nasheed) Emotional Speech ! Mohamed Hoblos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DW-00ckCAPI</t>
+          <t>https://www.youtube.com/watch?v=UsUq1YOWLoA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>58m 43s</t>
+          <t>17m 8s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The World's First AI-Visualized Sirah Series - Official Trailer - O MESSENGER</t>
+          <t>Don't Stop ! Push Yourself the Whole Ramadan ! Emotional Speech ! Mohamed Hoblos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sQMC7fkjmOA</t>
+          <t>https://www.youtube.com/watch?v=a0Q9Xf_ZS1E</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2m 38s</t>
+          <t>17m 8s</t>
         </is>
       </c>
     </row>
@@ -1764,110 +2352,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ep 9: Beauty, Care and Being Loved | Surah Ar-Rahman: A Deeper Look | Nouman Ali Khan | Ramadan 2026</t>
+          <t>Islam vs. Judaism - Which AI Won the Debate?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RSySaKOxvls</t>
+          <t>https://www.youtube.com/watch?v=lbbgie0gF_A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25m 14s</t>
+          <t>26m 47s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[Urdu] Ep 9: Shukr Is Easier Than You Think | Allamal Quran: A Study of Surah Ar-Rahman | Ramada 26</t>
+          <t>Shocking Miracles in the Air Hidden by Allah - The End of Atheism!</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xY-zVjkPbbw</t>
+          <t>https://www.youtube.com/watch?v=_4A8HkfHNBU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25m 31s</t>
+          <t>12m 17s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ep 8: Don’t Violate the Balance | Surah Ar-Rahman: A Deeper Look | Ramadan 26</t>
+          <t>Islam vs. Buddhism &amp; Hinduism: The Great AI Debate! - Who Won?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2Ec6jH1oWts</t>
+          <t>https://www.youtube.com/watch?v=CVyXVQzirYg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28m 37s</t>
+          <t>13m 32s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[Urdu] Ep 8: فَبِأَيِّ آلَاءِ رَبِّكُمَا تُكَذِّبَان Why Does Allah Keep Asking This Question?</t>
+          <t>“My Hindu Girlfriend Led me Back to Islam” - Emotional Life Story of @The Sunnah Guy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aN8LqGIDy9U</t>
+          <t>https://www.youtube.com/watch?v=A-xPS0uZY7c</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21m 8s</t>
+          <t>24m 3s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ep 7: Everything Lowers Itself, Everything Is Measured | Surah Ar-Rahman: A Deeper Look | Ramadan 26</t>
+          <t>The Prophet’s Farewell to the World! His Final Words to You! | Final Episode - O Messenger</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kdLlyP5KBxU</t>
+          <t>https://www.youtube.com/watch?v=pR65Sfhp-AY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32m 41s</t>
+          <t>40m 57s</t>
         </is>
       </c>
     </row>

--- a/all_channels.xlsx
+++ b/all_channels.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Repos\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F08A1A5-6DE9-439D-9F96-CFF2F7DADBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623C727E-B415-4EA0-877A-DB6CA9D5EB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rihla" sheetId="14" r:id="rId1"/>
+    <sheet name="Safina Society" sheetId="12" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -39,64 +39,64 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>Prophet's ﷺ Answer That Rewrote a Man's Entire Destiny - Shaykh Abdal Hakim Murad</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=EO3IkTG7G4g</t>
-  </si>
-  <si>
-    <t>25m 23s</t>
-  </si>
-  <si>
-    <t>Imam Ali's Final Hours - The Fitnah Explained - Shaykh Abdal Hakim Murad</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=f3LKGO3KkQs</t>
-  </si>
-  <si>
-    <t>27m 29s</t>
-  </si>
-  <si>
-    <t>Prophet's Warning About Two Faced Venomous People - Shaykh Abdal Hakim Murad</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=dBVz-oszLHA</t>
-  </si>
-  <si>
-    <t>26m 55s</t>
-  </si>
-  <si>
-    <t>The Dangerous Pleasure of Talking About People - Shaykh Abdal Hakim Murad</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=5Q1r8XF9yCs</t>
-  </si>
-  <si>
-    <t>36m 21s</t>
-  </si>
-  <si>
-    <t>The Sin That Makes You Look Like A Hypocrite - Shaykh Abdal Hakim Murad</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=W2tqupoGx-o</t>
-  </si>
-  <si>
-    <t>54m 2s</t>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>Why “Religious” Isn’t Enough for Marriage (The Hidden Problem)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=z3iGzZWDm8o</t>
+  </si>
+  <si>
+    <t>12m 28s</t>
+  </si>
+  <si>
+    <t>30-Year Study Proves Unlimited Freedom Causes Anxiety | Dr Shadee Elmasry</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RurKSyYl8o0</t>
+  </si>
+  <si>
+    <t>8m 40s</t>
+  </si>
+  <si>
+    <t>What to Do After a Baby Is Born in Islam (Maliki Fiqh) | Dr Shadee Elmasry</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7wHq0MRjKNk</t>
+  </si>
+  <si>
+    <t>8m 33s</t>
+  </si>
+  <si>
+    <t>What the Athari Creed Actually Says (Ibn Hamdan) | Dr Shadee Elmasry</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VUyXnOCixUA</t>
+  </si>
+  <si>
+    <t>10m 53s</t>
+  </si>
+  <si>
+    <t>Are Muslims Repeating Christian Mistakes? Dr Shadee Responds</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SUgJHYhICQM</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>14m 13s</t>
   </si>
 </sst>
 </file>
@@ -442,11 +442,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="72.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -464,70 +464,70 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>

--- a/all_channels.xlsx
+++ b/all_channels.xlsx
@@ -8,12 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Repos\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAC4A7E-FCC3-436B-B4EA-DA3428BB0EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFE9C4E-7300-4B2C-8F47-0E71830C2DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Safina Society" sheetId="12" r:id="rId1"/>
+    <sheet name="Abu Bakr Zoud" sheetId="1" r:id="rId1"/>
+    <sheet name="Arabic 101" sheetId="3" r:id="rId2"/>
+    <sheet name="Khalid Mehmood Abbasi" sheetId="4" r:id="rId3"/>
+    <sheet name="Yaqeen Institute" sheetId="5" r:id="rId4"/>
+    <sheet name="Tarteel AI" sheetId="6" r:id="rId5"/>
+    <sheet name="Towards Eternity" sheetId="9" r:id="rId6"/>
+    <sheet name="Bayyinah Institute" sheetId="10" r:id="rId7"/>
+    <sheet name="Safina Society" sheetId="12" r:id="rId8"/>
+    <sheet name="Blogging Theology" sheetId="14" r:id="rId9"/>
+    <sheet name="Francesca Bocca-Aldaqre" sheetId="15" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="177">
   <si>
     <t>Title</t>
   </si>
@@ -39,64 +48,523 @@
     <t>Duration</t>
   </si>
   <si>
+    <t>Reflections from the Revelation | EP10 | Maryam: A Role Model For Mankind | Abu Bakr Zoud</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3hIDUCipPNE</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>14m 10s</t>
+  </si>
+  <si>
+    <t>One of the Most Important Dua in your Prayer | Abu Bakr Zoud</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FAihyciqXCU</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>3m 40s</t>
+  </si>
+  <si>
+    <t>Ashura, Don’t Miss This Day | Abu Bakr Zoud</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NBnLg7pnj2c</t>
+  </si>
+  <si>
     <t>2026-06-24</t>
   </si>
   <si>
+    <t>3m 27s</t>
+  </si>
+  <si>
+    <t>The Greatness of the Day of Arafah | Khutbah Arafah | Abu Bakr Zoud</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mvh00eUjMzk</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>27m 0s</t>
+  </si>
+  <si>
+    <t>Not at Hajj? Start the Fajr of the Day of Arafah With This | Abu Bakr Zoud</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TwptteAd5gI</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>3m 46s</t>
+  </si>
+  <si>
+    <t>TikTok 'Say Wallahi' Trend Is Hiding Something Darker | Arabic101</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Df3RuzTj_s0</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>8m 17s</t>
+  </si>
+  <si>
+    <t>How to Understand Hadith Terminology in 10 Minutes | Arabic101</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pKLH49CAZI4</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>10m 54s</t>
+  </si>
+  <si>
+    <t>The Quran vs. The Telephone Game | Arabic101</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=T_8YI2M-aN4</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>10m 41s</t>
+  </si>
+  <si>
+    <t>What Happens When You Pause in the Wrong Place in the Quran? | Lesson 2 | Arabic101</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dAhgpvNB8vE</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>8m 39s</t>
+  </si>
+  <si>
+    <t>The Amazonian Tribe That Accidentally Proved the Quran is Unmatched | Arabic101</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=phO4YyNJ244</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>11m 53s</t>
+  </si>
+  <si>
+    <t>Violence or Peaceful Struggle? | Which Path Leads to Lasting Success? | Khalid Mehmood Abbasi</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ErAuHaEKpzA</t>
+  </si>
+  <si>
+    <t>74m 30s</t>
+  </si>
+  <si>
+    <t>BLA &amp; TTP Alliance? | Kashmir’s Political Future and the Fate of the Protest Movement</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-cQzZBbmbyY</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>91m 46s</t>
+  </si>
+  <si>
+    <t>Shukr to Allah: The Foundation of Inner Peace and Global Harmony | Khalid Mehmood Abbasi</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9o_Ip7XGFCE</t>
+  </si>
+  <si>
+    <t>30m 2s</t>
+  </si>
+  <si>
+    <t>Azad Kashmir's Turning Point: Genuine Reforms or a New Political Experiment? | Tazkara o Tabsara</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=l0BT4nr1Yek</t>
+  </si>
+  <si>
+    <t>96m 24s</t>
+  </si>
+  <si>
+    <t>The Role of Nonviolence in People’s Movements | Strategy, Discipline &amp; Lasting Change</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4xzvVYtfMdg</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>59m 39s</t>
+  </si>
+  <si>
+    <t>When Muslim Debates Become Destructive | Imam Tom Weekly</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yypIsa-5eJs</t>
+  </si>
+  <si>
+    <t>10m 36s</t>
+  </si>
+  <si>
+    <t>4 Voices the Prophet ﷺ Told Us Not to Follow | Signs of the Hour Ep. 11 | Dr. Omar Suleiman</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=cQ_3AvSodU8</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>27m 14s</t>
+  </si>
+  <si>
+    <t>Abu Mihjan (ra): The Sahabi With A Substance Use Disorder | The Firsts | Dr. Omar Suleiman</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9aXoVumS_Tk</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>19m 44s</t>
+  </si>
+  <si>
+    <t>Srebrenica, Up Close and Personal | Dr. Omar Suleiman</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dsrkp1KhXG8</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>12m 2s</t>
+  </si>
+  <si>
+    <t>The Gambling Industry Inside Your Pocket | Focal Point | Imam Tom Facchine</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xXYYGreE7XI</t>
+  </si>
+  <si>
+    <t>41m 42s</t>
+  </si>
+  <si>
+    <t>Do This for 30 Days and CHANGE Your Life | Sh. Ali Hammuda | Islah Ep. 4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4cXm6yN6O5o</t>
+  </si>
+  <si>
+    <t>12m 3s</t>
+  </si>
+  <si>
+    <t>What Scared The Most Powerful Men Alive? | Sh. Ali Hammuda | Islah Ep. 3</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pcjwUk1cd78</t>
+  </si>
+  <si>
     <t>2026-07-03</t>
   </si>
   <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
+    <t>14m 56s</t>
+  </si>
+  <si>
+    <t>How The Quran Liberates You | Sh. Ali Hammuda | Islah Ep. 2</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_f3I31mKLKI</t>
   </si>
   <si>
     <t>2026-06-26</t>
   </si>
   <si>
-    <t>How to Remove Riba From Your Life (From an Ex-Morgan Stanley Investment Banker)</t>
+    <t>11m 32s</t>
+  </si>
+  <si>
+    <t>How Muslims Can Prepare For EVERY Test In Life | Sheikh Ali Hammuda | Islah Ep.1</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fNkG5rA_3v0</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>13m 19s</t>
+  </si>
+  <si>
+    <t>ISLAH | Official Trailer | Featuring Sheikh Ali Hammuda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KbdJ_SC215o</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>0m 57s</t>
+  </si>
+  <si>
+    <t>309 Years Asleep! The Quranic Miracle of Ashab al-Kahf | AI Visualized</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZkPLWivmPYg</t>
+  </si>
+  <si>
+    <t>14m 58s</t>
+  </si>
+  <si>
+    <t>"I Left My Medical Career for Islam" - The Untold Story Behind Towards Eternity</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yeEI3Q2v-Ro</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>19m 17s</t>
+  </si>
+  <si>
+    <t>Was Islam Spread By The Sword? - Shocking Data Destroys the Myth!</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nLlTw2fnk-Y</t>
+  </si>
+  <si>
+    <t>16m 29s</t>
+  </si>
+  <si>
+    <t>An Atheist Converts to Islam: "My Mother’s Tragic D*ath Led Me to Islam”</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ma9Z1dDqCp0</t>
+  </si>
+  <si>
+    <t>27m 2s</t>
+  </si>
+  <si>
+    <t>"My Friend Stabbed Me, and Left Me to Die!" - From Crime to Islam | Tearful Story of Akhi Ayman</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BSs0NQIxFxM</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>22m 47s</t>
+  </si>
+  <si>
+    <t>What Mary’s Story Teaches Us About Judging Others | Q&amp;A with Nouman Ali Khan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JwcPKwYbDlM</t>
+  </si>
+  <si>
+    <t>5m 48s</t>
+  </si>
+  <si>
+    <t>Why Reading Into What People Say Poisons Your Heart | Surah Al-Hujurat | Nouman Ali Khan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=u79qO2xUC6I</t>
+  </si>
+  <si>
+    <t>14m 25s</t>
+  </si>
+  <si>
+    <t>Selective Outrage: Standing Up Against Injustice | Q&amp;A with Nouman Ali Khan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=44CjakYyqSY</t>
+  </si>
+  <si>
+    <t>6m 34s</t>
+  </si>
+  <si>
+    <t>Your Sarcastic Compliment Is Still an Insult | Surah Al-Hujurat | Nouman Ali Khan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=21QmoJUpEeI</t>
+  </si>
+  <si>
+    <t>22m 27s</t>
+  </si>
+  <si>
+    <t>How Long Will My Oppressors Keep Getting Away With It? | Q&amp;A with Nouman Ali Khan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PpO0um4q8Ig</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>7m 58s</t>
+  </si>
+  <si>
+    <t>Ibn Taymiyyah Recorded the Sahaba Saying "Ya Muhammad"</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=a-caOKMkxgk</t>
+  </si>
+  <si>
+    <t>13m 10s</t>
+  </si>
+  <si>
+    <t>Will Non-Muslims Be Judged for Not Praying &amp; Fasting?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ldma_SiVSRU</t>
+  </si>
+  <si>
+    <t>8m 24s</t>
+  </si>
+  <si>
+    <t>The 2 Types of Sadness in the Quran (One Is From Shaytan)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fLIiMcNpyDo</t>
+  </si>
+  <si>
+    <t>10m 9s</t>
+  </si>
+  <si>
+    <t>Salafis vs. Sufis: What Would the Prophet ﷺ Say?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3a322F6e-Zw</t>
+  </si>
+  <si>
+    <t>11m 18s</t>
+  </si>
+  <si>
+    <t>3 Steps to Remove Riba From Your Life (From an Ex-Investment Banker)</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=z_yMztX4AJQ</t>
   </si>
   <si>
-    <t>11m 18s</t>
-  </si>
-  <si>
-    <t>What Did the Prophet Muhammad ﷺ Look Like?</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=mROOycg_MwA</t>
-  </si>
-  <si>
-    <t>14m 36s</t>
-  </si>
-  <si>
-    <t>Shaytan's Most Dangerous Trap (Even Religious Muslims Fall Into It)</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=1zGUhhFJcsw</t>
-  </si>
-  <si>
-    <t>9m 1s</t>
-  </si>
-  <si>
-    <t>The 7 Human Desires That Control Your Life (Islam Explains Them Perfectly)</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=C0tQcRfq-HU</t>
-  </si>
-  <si>
-    <t>23m 59s</t>
-  </si>
-  <si>
-    <t>When Spirituality Becomes a Performance | Dr Shadee Elmasry</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=-Y62aAbNl0g</t>
-  </si>
-  <si>
-    <t>8m 31s</t>
+    <t>Everything You Think You Know About Jihadi-Salafism Is Wrong? | Jaan Islam Explains</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9x1Urmo10dw</t>
+  </si>
+  <si>
+    <t>68m 33s</t>
+  </si>
+  <si>
+    <t>The Prophet's Secret to Multiplying Time | Adnan Adrian Wood-Smith ⭐</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mimY480A1VQ</t>
+  </si>
+  <si>
+    <t>61m 10s</t>
+  </si>
+  <si>
+    <t>The Unfortunate Truth About the Muslim Grooming Gangs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qBUZuFUseJo</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>4m 17s</t>
+  </si>
+  <si>
+    <t>How Bible Scholars Challenged my Christian Faith</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vTfxQlraBMA</t>
+  </si>
+  <si>
+    <t>25m 54s</t>
+  </si>
+  <si>
+    <t>Did Muhammad Iqbal Reject Nationalism? His Most Misunderstood Poem | Dr. Asif Hirani</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qlPhrjEIwko</t>
+  </si>
+  <si>
+    <t>45m 16s</t>
+  </si>
+  <si>
+    <t>Why You Feel "Not Muslim Enough" | Riya, Nafs al-Lawwama &amp; Sincerity in Islam</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SMIRU09YOcM</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>15m 10s</t>
+  </si>
+  <si>
+    <t>The Hidden Cause of Doubt | How Your Environment Shapes Your Iman | Imam Al-Ghazali | Dr Francesca</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0g-lGGLVr7I</t>
+  </si>
+  <si>
+    <t>23m 10s</t>
+  </si>
+  <si>
+    <t>The Only Person You Can Diagnose Is Yourself | Islamic Psychology | | Dr Francesca</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KZ8xqWPq0X4</t>
+  </si>
+  <si>
+    <t>8m 3s</t>
+  </si>
+  <si>
+    <t>What Is Narcissism? An Islamic Psychology Perspective | The common signs or traits of narcissism |</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=b46qKes2u20</t>
+  </si>
+  <si>
+    <t>15m 54s</t>
+  </si>
+  <si>
+    <t>I Studied Neuroscience &amp; CBT | Why I Chose Islamic Psychology | What is the Condition of Your Heart?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6638IDcYt0o</t>
+  </si>
+  <si>
+    <t>10m 5s</t>
   </si>
 </sst>
 </file>
@@ -112,12 +580,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -134,7 +608,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,11 +910,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="78.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -459,72 +933,945 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
       </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="87.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="74.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="83" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="78.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="69.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="81.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="77.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="60.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
+      <c r="A6" t="s">
+        <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
